--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T2_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>72</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,127 +72,127 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.64e+05</t>
-  </si>
-  <si>
-    <t>(72511.429)</t>
-  </si>
-  <si>
-    <t>489.096</t>
-  </si>
-  <si>
-    <t>(34.780)</t>
-  </si>
-  <si>
-    <t>3.616</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
   </si>
   <si>
     <t>(0.048)</t>
   </si>
   <si>
-    <t>10.123</t>
-  </si>
-  <si>
-    <t>(1.887)</t>
-  </si>
-  <si>
-    <t>88.196</t>
-  </si>
-  <si>
-    <t>(0.488)</t>
-  </si>
-  <si>
-    <t>1.03e+06</t>
-  </si>
-  <si>
-    <t>(56763.318)</t>
-  </si>
-  <si>
-    <t>2.478</t>
-  </si>
-  <si>
-    <t>(0.134)</t>
-  </si>
-  <si>
-    <t>3.288</t>
-  </si>
-  <si>
-    <t>(0.467)</t>
-  </si>
-  <si>
-    <t>33.863</t>
-  </si>
-  <si>
-    <t>(3.744)</t>
-  </si>
-  <si>
-    <t>0.945</t>
-  </si>
-  <si>
-    <t>(0.027)</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6.99e+05</t>
-  </si>
-  <si>
-    <t>(1.26e+05)</t>
-  </si>
-  <si>
-    <t>498.644</t>
-  </si>
-  <si>
-    <t>(52.491)</t>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
   </si>
   <si>
     <t>3.352</t>
   </si>
   <si>
-    <t>(0.055)</t>
-  </si>
-  <si>
-    <t>26.047</t>
-  </si>
-  <si>
-    <t>(3.793)</t>
-  </si>
-  <si>
-    <t>91.268</t>
-  </si>
-  <si>
-    <t>(0.450)</t>
-  </si>
-  <si>
-    <t>1.34e+06</t>
-  </si>
-  <si>
-    <t>(68157.305)</t>
-  </si>
-  <si>
-    <t>3.292</t>
-  </si>
-  <si>
-    <t>(0.140)</t>
-  </si>
-  <si>
-    <t>5.930</t>
-  </si>
-  <si>
-    <t>(0.584)</t>
-  </si>
-  <si>
-    <t>42.326</t>
-  </si>
-  <si>
-    <t>(3.283)</t>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.35e+05</t>
-  </si>
-  <si>
-    <t>9.548</t>
-  </si>
-  <si>
-    <t>-0.264***</t>
-  </si>
-  <si>
-    <t>15.923***</t>
-  </si>
-  <si>
-    <t>3.072***</t>
-  </si>
-  <si>
-    <t>3.10e+05***</t>
-  </si>
-  <si>
-    <t>0.814***</t>
-  </si>
-  <si>
-    <t>2.643***</t>
-  </si>
-  <si>
-    <t>8.463</t>
-  </si>
-  <si>
-    <t>0.055</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T2_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>73</t>
+  </si>
+  <si>
+    <t>72</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.64e+05</t>
+  </si>
+  <si>
+    <t>(72511.429)</t>
+  </si>
+  <si>
+    <t>489.096</t>
+  </si>
+  <si>
+    <t>(34.780)</t>
+  </si>
+  <si>
+    <t>3.616</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>10.123</t>
+  </si>
+  <si>
+    <t>(1.887)</t>
+  </si>
+  <si>
+    <t>88.196</t>
+  </si>
+  <si>
+    <t>(0.488)</t>
+  </si>
+  <si>
+    <t>1.03e+06</t>
+  </si>
+  <si>
+    <t>(56763.318)</t>
+  </si>
+  <si>
+    <t>2.478</t>
+  </si>
+  <si>
+    <t>(0.134)</t>
+  </si>
+  <si>
+    <t>3.288</t>
+  </si>
+  <si>
+    <t>(0.467)</t>
+  </si>
+  <si>
+    <t>33.863</t>
+  </si>
+  <si>
+    <t>(3.744)</t>
+  </si>
+  <si>
+    <t>0.945</t>
+  </si>
+  <si>
+    <t>(0.027)</t>
+  </si>
+  <si>
+    <t>43</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
+    <t>6.99e+05</t>
+  </si>
+  <si>
+    <t>(1.26e+05)</t>
+  </si>
+  <si>
+    <t>498.644</t>
+  </si>
+  <si>
+    <t>(52.491)</t>
   </si>
   <si>
     <t>3.352</t>
   </si>
   <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>26.047</t>
+  </si>
+  <si>
+    <t>(3.793)</t>
+  </si>
+  <si>
+    <t>91.268</t>
+  </si>
+  <si>
+    <t>(0.450)</t>
+  </si>
+  <si>
+    <t>1.34e+06</t>
+  </si>
+  <si>
+    <t>(68157.305)</t>
+  </si>
+  <si>
+    <t>3.292</t>
+  </si>
+  <si>
+    <t>(0.140)</t>
+  </si>
+  <si>
+    <t>5.930</t>
+  </si>
+  <si>
+    <t>(0.584)</t>
+  </si>
+  <si>
+    <t>42.326</t>
+  </si>
+  <si>
+    <t>(3.283)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.35e+05</t>
+  </si>
+  <si>
+    <t>9.548</t>
+  </si>
+  <si>
+    <t>-0.264***</t>
+  </si>
+  <si>
+    <t>15.923***</t>
+  </si>
+  <si>
+    <t>3.072***</t>
+  </si>
+  <si>
+    <t>3.10e+05***</t>
+  </si>
+  <si>
+    <t>0.814***</t>
+  </si>
+  <si>
+    <t>2.643***</t>
+  </si>
+  <si>
+    <t>8.463</t>
+  </si>
+  <si>
+    <t>0.055</t>
   </si>
 </sst>
 </file>
